--- a/figs/data/fig7_mixU_v4.xlsx
+++ b/figs/data/fig7_mixU_v4.xlsx
@@ -310,135 +310,6 @@
           </yVal>
           <smooth val="0"/>
         </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'학습 (후보 수)'!K1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'학습 (후보 수)'!$J$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'학습 (후보 수)'!$K$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'학습 (후보 수)'!M1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'학습 (후보 수)'!$L$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'학습 (후보 수)'!$M$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'학습 (후보 수)'!O1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'학습 (후보 수)'!$N$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'학습 (후보 수)'!$O$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
         <axId val="10"/>
         <axId val="20"/>
       </scatterChart>
@@ -503,26 +374,6 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
-      <legendEntry>
-        <idx val="2"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="3"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="4"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="5"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="6"/>
-        <delete val="1"/>
-      </legendEntry>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -534,7 +385,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>16</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -846,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X293"/>
+  <dimension ref="A1:R293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,52 +723,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>선1 x</t>
+          <t>→ 2회차 Varmail+FIO-Fast x</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>선1</t>
+          <t>→ 2회차 Varmail+FIO-Fast</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>선2 x</t>
+          <t>→ 3회차 Varmail+FIO-Fast+Varmail+FIO-Fast+Varmail x</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>선2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>라벨1 x</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>1회차 FIO-Fast</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>라벨2 x</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>2회차 Varmail+FIO-Fast</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>라벨3 x</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>3회차 Varmail+FIO-Fast+Varmail+FIO-Fast+Varmail</t>
+          <t>→ 3회차 Varmail+FIO-Fast+Varmail+FIO-Fast+Varmail</t>
         </is>
       </c>
     </row>
@@ -946,24 +767,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>48</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>48</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>48</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1396,42 +1199,42 @@
       <c r="D32" t="n">
         <v>10</v>
       </c>
-      <c r="Q32" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>회차</t>
         </is>
       </c>
-      <c r="R32" s="1" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>워크로드</t>
         </is>
       </c>
-      <c r="S32" s="1" t="inlineStr">
+      <c r="M32" s="1" t="inlineStr">
         <is>
           <t>시작(h)</t>
         </is>
       </c>
-      <c r="T32" s="1" t="inlineStr">
+      <c r="N32" s="1" t="inlineStr">
         <is>
           <t>끝(h)</t>
         </is>
       </c>
-      <c r="U32" s="1" t="inlineStr">
+      <c r="O32" s="1" t="inlineStr">
         <is>
           <t>시험 횟수</t>
         </is>
       </c>
-      <c r="V32" s="1" t="inlineStr">
+      <c r="P32" s="1" t="inlineStr">
         <is>
           <t>처음 후보</t>
         </is>
       </c>
-      <c r="W32" s="1" t="inlineStr">
+      <c r="Q32" s="1" t="inlineStr">
         <is>
           <t>최소 후보</t>
         </is>
       </c>
-      <c r="X32" s="1" t="inlineStr">
+      <c r="R32" s="1" t="inlineStr">
         <is>
           <t>마지막 최고 후보</t>
         </is>
@@ -1450,30 +1253,30 @@
       <c r="D33" t="n">
         <v>6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>1.FIO-Fast</t>
         </is>
       </c>
-      <c r="S33" t="n">
+      <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="T33" t="n">
+      <c r="N33" t="n">
         <v>1.32</v>
       </c>
-      <c r="U33" t="n">
+      <c r="O33" t="n">
         <v>323</v>
       </c>
-      <c r="V33" t="n">
+      <c r="P33" t="n">
         <v>45</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Q33" t="n">
         <v>11</v>
       </c>
-      <c r="X33" t="n">
+      <c r="R33" t="n">
         <v>46</v>
       </c>
     </row>
@@ -1490,30 +1293,30 @@
       <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="Q34" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>2.Varmail+3.FIO-Fast</t>
         </is>
       </c>
-      <c r="S34" t="n">
+      <c r="M34" t="n">
         <v>1.32</v>
       </c>
-      <c r="T34" t="n">
+      <c r="N34" t="n">
         <v>3.76</v>
       </c>
-      <c r="U34" t="n">
+      <c r="O34" t="n">
         <v>1136</v>
       </c>
-      <c r="V34" t="n">
+      <c r="P34" t="n">
         <v>20</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Q34" t="n">
         <v>5</v>
       </c>
-      <c r="X34" t="n">
+      <c r="R34" t="n">
         <v>47</v>
       </c>
     </row>
@@ -1530,30 +1333,30 @@
       <c r="D35" t="n">
         <v>4</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3</v>
-      </c>
-      <c r="R35" t="inlineStr">
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>4.Varmail+5.FIO-Fast+6.Varmail+7.FIO-Fast+8.Varmail</t>
         </is>
       </c>
-      <c r="S35" t="n">
+      <c r="M35" t="n">
         <v>3.76</v>
       </c>
-      <c r="T35" t="n">
+      <c r="N35" t="n">
         <v>10</v>
       </c>
-      <c r="U35" t="n">
+      <c r="O35" t="n">
         <v>3093</v>
       </c>
-      <c r="V35" t="n">
+      <c r="P35" t="n">
         <v>13</v>
       </c>
-      <c r="W35" t="n">
-        <v>3</v>
-      </c>
-      <c r="X35" t="n">
+      <c r="Q35" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" t="n">
         <v>47</v>
       </c>
     </row>

--- a/figs/data/fig7_mixU_v4.xlsx
+++ b/figs/data/fig7_mixU_v4.xlsx
@@ -205,9 +205,6 @@
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
               <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
